--- a/plantillas/plantilla_informe_mensual.xlsx
+++ b/plantillas/plantilla_informe_mensual.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ejecucion" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Pagos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Control" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,11 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F4C45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -74,6 +83,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -483,6 +495,13 @@
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Panel → Finanzas → Informe mensual: cargue el archivo, elija año y mes y escriba los totales del informe contable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hoja Control (celdas amarillas): la llena la contadora con los totales del informe contable. La usa el programa del PC de la administración; en el panel, los totales se escriben a mano.</t>
         </is>
       </c>
     </row>
@@ -1128,4 +1147,112 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>dato</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>qué es</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Año del informe (ej.: 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mes del informe, en número (1 a 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_ingresos</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Total de ingresos del mes según el informe contable</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>total_gastos</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Total de gastos del mes según el informe contable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_pagos</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Total de pagos del mes (flujo de caja). Solo si la hoja Pagos tiene filas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Si los totales de las hojas no son iguales a estos valores, no se publica nada.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>